--- a/Översikt KARLSHAMN.xlsx
+++ b/Översikt KARLSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>44897</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45170</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>46218</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>46150</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45376</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45310</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>44497</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>45187</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>45934</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>46211</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>46184</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>44621</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45603</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>46092</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>45028</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>45169</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>44897</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>46092</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>44595</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>45068</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>44901</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>44943</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>45782</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>44655</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44862</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>45118</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>46282</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>45826</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>45104</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>45898</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>46121</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>44722</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>44680</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>44476</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>44812</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>44525</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>44579</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>44563</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>44470</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>44509</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>44480</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>44834</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>44742</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>44579</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>44834</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>44563</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>44581</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44462</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>44523</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>44470</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>44582</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44776</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>44489</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>44776</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>44580</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44796</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>44522</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>44489</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>44489</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>44525</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>44526</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>44484</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>44487</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>44812</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>44743</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>45119</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>45351</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>44680</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>45007</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>45611</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>44903</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>45205</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>45051</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>45051</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>45412</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>45448</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>44962</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>45246</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>45246</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>45180</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>45219</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>44895</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>44935</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>44952</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>44952</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>45550</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>44686</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>44845</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>45636</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>44797</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         <v>45028</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         <v>45187</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>45166</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>44649</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>44480</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>45266</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>45461</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>45429</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>45687</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>45212</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>44983</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>44970</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>45229</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>45601</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>45205</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>45205</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>45632</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>45400</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>45108</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>44624</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>45468</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>45114</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>45240</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>45310</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>45841</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>45884</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>44568</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>45732</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>45553</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>44462</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>45716</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         <v>45072</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         <v>45114</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>44812</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>45846</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         <v>45789</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>45501</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         <v>45254</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>45898</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11148,7 +11148,7 @@
         <v>45898</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>45898</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         <v>44797</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>45035</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         <v>45870</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>45744</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11596,7 +11596,7 @@
         <v>45717</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>45848</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>45905</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>45908</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>45908</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>44897</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>45219</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>45782</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>45898</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>45911</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>45439</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>45152</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>45540</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>45918</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>44959</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12706,7 +12706,7 @@
         <v>45405</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12779,7 +12779,7 @@
         <v>45270</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
         <v>45926</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
         <v>45911</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>45926</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>45225</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>45330</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13217,7 +13217,7 @@
         <v>45238</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>45148</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13363,7 +13363,7 @@
         <v>45937</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>46051</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13509,7 +13509,7 @@
         <v>45939</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>46149</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         <v>45279</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>45950</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>45953</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>45954</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>45118</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>44923</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>45580</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14166,7 +14166,7 @@
         <v>45106</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>44622</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14312,7 +14312,7 @@
         <v>44518</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>45090</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         <v>45967</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>45967</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
         <v>45457</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>45163</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14765,7 +14765,7 @@
         <v>45519</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         <v>45846</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>45091</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>45722</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         <v>45037</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15130,7 +15130,7 @@
         <v>44480</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>45981</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>45981</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         <v>44981</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>45986</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>46161</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15573,7 +15573,7 @@
         <v>44568</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>44607</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>45917</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15792,7 +15792,7 @@
         <v>45770</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15865,7 +15865,7 @@
         <v>44525</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15938,7 +15938,7 @@
         <v>44531</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
         <v>46164</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16084,7 +16084,7 @@
         <v>46001</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>46001</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>45757</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         <v>46164</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>46164</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>44571</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>45894</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>45903</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>45894</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16751,7 +16751,7 @@
         <v>45009</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>45376</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>45148</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16970,7 +16970,7 @@
         <v>45307</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
         <v>45056</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>45607</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>45631</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>44609</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>46170</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17408,7 +17408,7 @@
         <v>45054</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         <v>44812</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17554,7 +17554,7 @@
         <v>46170</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>46170</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>46170</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>46170</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>45068</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>45967</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>46041</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>45740</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>45617</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>46174</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>44533</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>46055</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18440,7 +18440,7 @@
         <v>46181</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>45987</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>46181</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>45502</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>46181</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>45138</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
         <v>45079</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18951,7 +18951,7 @@
         <v>44530</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19024,7 +19024,7 @@
         <v>44971</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>46083</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
         <v>45373</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>46090</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>46190</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>46001</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19467,7 +19467,7 @@
         <v>44943</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         <v>45114</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>45550</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19686,7 +19686,7 @@
         <v>44742</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>46097</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19832,7 +19832,7 @@
         <v>44827</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>45519</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19978,7 +19978,7 @@
         <v>45243</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>46097</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20124,7 +20124,7 @@
         <v>45104</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>46191</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20270,7 +20270,7 @@
         <v>46196</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
         <v>46100</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>44823</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>46104</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>45307</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>46106</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>46106</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>44939</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20864,7 +20864,7 @@
         <v>44939</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
         <v>44939</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21010,7 +21010,7 @@
         <v>44760</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>45824</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>45953</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>45953</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>46113</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21375,7 +21375,7 @@
         <v>46113</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21448,7 +21448,7 @@
         <v>46113</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         <v>44943</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>44952</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>45147</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>46122</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>45439</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>46202</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21959,7 +21959,7 @@
         <v>46202</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22032,7 +22032,7 @@
         <v>46245</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22110,7 +22110,7 @@
         <v>44924</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>45148</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22256,7 +22256,7 @@
         <v>44623</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>45884</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22402,7 +22402,7 @@
         <v>45743</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22475,7 +22475,7 @@
         <v>45588</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22548,7 +22548,7 @@
         <v>45918</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22621,7 +22621,7 @@
         <v>45225</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22694,7 +22694,7 @@
         <v>45151</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22767,7 +22767,7 @@
         <v>45937</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22840,7 +22840,7 @@
         <v>45975</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22913,7 +22913,7 @@
         <v>45919</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22986,7 +22986,7 @@
         <v>45631</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23059,7 +23059,7 @@
         <v>45197</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23132,7 +23132,7 @@
         <v>45754</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23205,7 +23205,7 @@
         <v>45163</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>45309</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23351,7 +23351,7 @@
         <v>45596</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>45596</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23497,7 +23497,7 @@
         <v>45567</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23570,7 +23570,7 @@
         <v>45565</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>46254</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23716,7 +23716,7 @@
         <v>45236</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23789,7 +23789,7 @@
         <v>46258</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>46258</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>46258</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>46258</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24081,7 +24081,7 @@
         <v>46258</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>45114</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44844</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>46258</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>44660</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24451,7 +24451,7 @@
         <v>45947</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24524,7 +24524,7 @@
         <v>44816</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24597,7 +24597,7 @@
         <v>44728</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24670,7 +24670,7 @@
         <v>45344</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>45400</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>44946</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>45943</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24962,7 +24962,7 @@
         <v>45943</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>45266</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25108,7 +25108,7 @@
         <v>46266</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>46269</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25254,7 +25254,7 @@
         <v>45412</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25332,7 +25332,7 @@
         <v>45782</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25405,7 +25405,7 @@
         <v>46273</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>46045</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25551,7 +25551,7 @@
         <v>46251</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>46274</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25697,7 +25697,7 @@
         <v>46274</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>46231</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>46232</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         <v>46261</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25989,7 +25989,7 @@
         <v>46045</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26062,7 +26062,7 @@
         <v>44609</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>45243</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26208,7 +26208,7 @@
         <v>46266</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>46237</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26354,7 +26354,7 @@
         <v>45943</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>46282</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>46282</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26573,7 +26573,7 @@
         <v>46282</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26646,7 +26646,7 @@
         <v>46282</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>45796</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>45104</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>45600</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>45805</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27011,7 +27011,7 @@
         <v>45810</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27084,7 +27084,7 @@
         <v>45813</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>45813</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>45813</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>45813</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>45813</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>45824</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>45824</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>45826</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27673,7 +27673,7 @@
         <v>45845</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27746,7 +27746,7 @@
         <v>45719</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27819,7 +27819,7 @@
         <v>45846</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27892,7 +27892,7 @@
         <v>45849</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27965,7 +27965,7 @@
         <v>45855</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>45737</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28111,7 +28111,7 @@
         <v>45841</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>45874</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28257,7 +28257,7 @@
         <v>44586</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>44230</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28403,7 +28403,7 @@
         <v>44621</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>45457</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>44959</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>45457</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>44959</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>45602</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>45575</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>44959</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>45733</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29060,7 +29060,7 @@
         <v>46069</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>46069</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>46069</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29279,7 +29279,7 @@
         <v>46071</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         <v>46092</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>46121</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>

--- a/Översikt KARLSHAMN.xlsx
+++ b/Översikt KARLSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>44897</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45170</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>46218</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>46150</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45310</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>45376</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>44497</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>45187</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>45934</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>46211</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>46184</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>44621</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45603</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>46092</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>45169</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>45028</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>44897</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>46092</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>44595</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>45782</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45068</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>44943</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>45826</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>45104</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44901</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>44655</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>46282</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>44862</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>45118</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>45898</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>46121</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>44722</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>44680</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>44812</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>44476</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>44525</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>44579</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>44563</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>44509</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>44470</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>44480</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>44834</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>44742</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>44579</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>44834</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>44563</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>44581</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44523</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>44582</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>44470</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>44489</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44776</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>44776</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>44580</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>44796</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44522</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>44489</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>44489</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>44525</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>44526</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>44484</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>44487</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>44812</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>45205</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>45412</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>45550</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>45240</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>45400</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>45400</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>44970</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>45796</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>45448</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>44895</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>44939</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>44939</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>45841</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>44981</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>44480</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>45967</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>46041</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>45600</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>45898</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>45898</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>45104</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7863,7 +7863,7 @@
         <v>45898</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>45870</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         <v>45351</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         <v>44939</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>45905</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>45908</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>45908</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8389,7 +8389,7 @@
         <v>45405</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
         <v>46055</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>44943</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         <v>45911</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>45918</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>45987</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>44623</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>44609</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>45926</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>45911</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         <v>45926</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>45550</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>45805</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>45051</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>45051</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
         <v>46083</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>45810</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>44660</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>46090</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9781,7 +9781,7 @@
         <v>45937</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>45939</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>46097</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>46097</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
         <v>45054</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>45205</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
         <v>45205</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>46100</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>45950</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>46104</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>44952</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>44952</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         <v>46106</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>46106</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>45824</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>45740</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10959,7 +10959,7 @@
         <v>45953</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>45953</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         <v>45953</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>45344</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>46113</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>46113</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>46113</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>45954</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>44943</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
         <v>45307</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
         <v>44971</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11767,7 +11767,7 @@
         <v>44946</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>46122</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>45601</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v>44952</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12059,7 +12059,7 @@
         <v>45967</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>45967</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>44903</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12288,7 +12288,7 @@
         <v>45813</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>45813</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>45813</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>45813</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>45813</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
         <v>45457</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>45254</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>45981</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>45981</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>45846</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>45743</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>44797</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>45986</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>45163</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>44649</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13383,7 +13383,7 @@
         <v>45884</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>45975</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>45918</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>45884</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>45035</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>45848</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>45717</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>45919</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13967,7 +13967,7 @@
         <v>45716</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>45151</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>45917</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>45147</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>45722</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>45553</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>45632</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>45588</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>45148</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>45138</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>45789</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>46001</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
         <v>46001</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>44812</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>45894</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>45894</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>45903</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>45937</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15291,7 +15291,7 @@
         <v>44823</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>44827</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15437,7 +15437,7 @@
         <v>45687</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>44845</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>45824</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>45037</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>45824</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>45732</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>45079</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>45246</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16021,7 +16021,7 @@
         <v>45246</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
         <v>45826</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>45898</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>45782</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>44924</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         <v>46051</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>45596</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>45596</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>46149</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>45540</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16761,7 +16761,7 @@
         <v>45631</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>44959</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>45846</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16980,7 +16980,7 @@
         <v>45770</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>45090</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>45229</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>46161</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>45846</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>46164</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>46164</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>45719</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>45845</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>45757</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>46164</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>45849</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>45855</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>46170</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>46170</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>46170</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>46170</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>45236</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45617</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>45166</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18440,7 +18440,7 @@
         <v>44935</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>46170</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>45148</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>45737</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>46174</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>44518</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18883,7 +18883,7 @@
         <v>45373</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>44480</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>45519</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>45212</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
         <v>46181</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>46181</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>45114</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>45429</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19467,7 +19467,7 @@
         <v>45009</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         <v>45841</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>45874</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19686,7 +19686,7 @@
         <v>46001</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>45580</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19832,7 +19832,7 @@
         <v>45180</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>46190</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19978,7 +19978,7 @@
         <v>46191</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>45056</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20124,7 +20124,7 @@
         <v>46196</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>44571</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20270,7 +20270,7 @@
         <v>45631</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
         <v>45636</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>44624</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>46202</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>44586</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>46202</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>44686</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>44816</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>45108</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>45114</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>45219</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>44568</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>46254</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>46258</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>45148</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>46258</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>46258</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>46258</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>45119</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>46258</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21730,7 +21730,7 @@
         <v>46258</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>45947</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         <v>44760</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>45307</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>44680</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>45754</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>45468</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
         <v>45187</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>45611</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>45943</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>45943</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>46266</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>45439</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>45243</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         <v>45225</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>46269</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22898,7 +22898,7 @@
         <v>46045</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>44844</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>45310</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45502</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>46273</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>46231</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>44812</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>45266</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>45225</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>46274</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>46274</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23706,7 +23706,7 @@
         <v>46232</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
         <v>45104</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>45565</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23925,7 +23925,7 @@
         <v>46237</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>46266</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>46045</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>45279</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>45943</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>46282</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>46282</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>44530</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>46282</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>46282</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>44797</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24728,7 +24728,7 @@
         <v>46245</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44983</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>45091</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
         <v>45330</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>44728</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>45501</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>45270</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>46251</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>46261</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>45106</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25463,7 +25463,7 @@
         <v>45607</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>44607</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25609,7 +25609,7 @@
         <v>44742</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>45114</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25755,7 +25755,7 @@
         <v>44568</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>45114</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25901,7 +25901,7 @@
         <v>45163</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>45028</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26047,7 +26047,7 @@
         <v>45376</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26120,7 +26120,7 @@
         <v>45007</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>45461</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26271,7 +26271,7 @@
         <v>45309</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>44525</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>45439</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>45266</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>45238</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>45068</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>44531</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26787,7 +26787,7 @@
         <v>44533</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26860,7 +26860,7 @@
         <v>45567</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26933,7 +26933,7 @@
         <v>45072</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>45197</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>44962</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>44743</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>45219</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>45152</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>44897</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>45118</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>44923</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>45519</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>44622</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>45412</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27819,7 +27819,7 @@
         <v>45782</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27892,7 +27892,7 @@
         <v>45243</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27965,7 +27965,7 @@
         <v>44609</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>44230</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28111,7 +28111,7 @@
         <v>44621</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>45457</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28257,7 +28257,7 @@
         <v>44959</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>45457</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28403,7 +28403,7 @@
         <v>44959</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>45602</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>45575</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>44959</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>45733</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>46069</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>46069</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>46069</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>46071</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29060,7 +29060,7 @@
         <v>46092</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>46121</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>

--- a/Översikt KARLSHAMN.xlsx
+++ b/Översikt KARLSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>44897</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45170</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>46218</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>46150</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45310</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>45376</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>44497</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>45187</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>45934</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>46211</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>46184</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>44621</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45603</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>46092</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>45169</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>45028</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>44897</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>46092</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>44595</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>45782</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45068</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>44943</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>45826</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>45104</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44901</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>44655</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>46282</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>44862</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>45118</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>45898</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>46121</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>44722</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>44680</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>44812</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>44476</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>44525</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>44579</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>44563</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>44509</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>44470</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>44480</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>44834</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>44742</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>44579</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>44834</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>44563</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>44581</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44523</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>44582</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>44470</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>44489</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44776</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>44776</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>44580</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>44796</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44522</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>44489</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>44489</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>44525</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>44526</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>44484</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>44487</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>44812</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>45205</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>45412</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>45550</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>45240</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>45400</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>45400</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>44970</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>45796</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>45448</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>44895</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>44939</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>44939</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>45841</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>44981</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>44480</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>45967</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>46041</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>45600</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>45898</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>45898</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>45104</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7863,7 +7863,7 @@
         <v>45898</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>45870</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         <v>45351</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         <v>44939</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>45905</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>45908</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>45908</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8389,7 +8389,7 @@
         <v>45405</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
         <v>46055</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>44943</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
         <v>45911</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>45918</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>45987</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>44623</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>44609</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>45926</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>45911</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         <v>45926</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>45550</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>45805</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>45051</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>45051</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
         <v>46083</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>45810</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>44660</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>46090</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9781,7 +9781,7 @@
         <v>45937</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>45939</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>46097</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>46097</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
         <v>45054</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>45205</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
         <v>45205</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>46100</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>45950</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>46104</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>44952</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>44952</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         <v>46106</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>46106</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>45824</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>45740</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10959,7 +10959,7 @@
         <v>45953</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>45953</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         <v>45953</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>45344</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>46113</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>46113</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>46113</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>45954</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>44943</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
         <v>45307</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
         <v>44971</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11767,7 +11767,7 @@
         <v>44946</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         <v>46122</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>45601</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v>44952</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12059,7 +12059,7 @@
         <v>45967</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>45967</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12215,7 +12215,7 @@
         <v>44903</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12288,7 +12288,7 @@
         <v>45813</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>45813</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12434,7 +12434,7 @@
         <v>45813</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>45813</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>45813</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
         <v>45457</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>45254</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12799,7 +12799,7 @@
         <v>45981</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12872,7 +12872,7 @@
         <v>45981</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>45846</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>45743</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>44797</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>45986</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>45163</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>44649</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13383,7 +13383,7 @@
         <v>45884</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>45975</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>45918</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>45884</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>45035</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>45848</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>45717</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>45919</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13967,7 +13967,7 @@
         <v>45716</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>45151</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>45917</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>45147</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>45722</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>45553</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>45632</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>45588</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>45148</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>45138</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>45789</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>46001</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
         <v>46001</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>44812</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>45894</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>45894</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>45903</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>45937</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15291,7 +15291,7 @@
         <v>44823</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>44827</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15437,7 +15437,7 @@
         <v>45687</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>44845</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>45824</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>45037</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>45824</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>45732</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>45079</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>45246</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16021,7 +16021,7 @@
         <v>45246</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
         <v>45826</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>45898</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>45782</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>44924</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         <v>46051</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>45596</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16542,7 +16542,7 @@
         <v>45596</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>46149</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>45540</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16761,7 +16761,7 @@
         <v>45631</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>44959</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>45846</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16980,7 +16980,7 @@
         <v>45770</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>45090</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>45229</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>46161</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>45846</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>46164</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>46164</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>45719</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>45845</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>45757</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>46164</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>45849</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>45855</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>46170</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>46170</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>46170</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>46170</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>45236</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45617</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>45166</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18440,7 +18440,7 @@
         <v>44935</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>46170</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>45148</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>45737</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>46174</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>44518</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18883,7 +18883,7 @@
         <v>45373</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>44480</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>45519</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>45212</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
         <v>46181</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>46181</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>45114</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>45429</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19467,7 +19467,7 @@
         <v>45009</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         <v>45841</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>45874</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19686,7 +19686,7 @@
         <v>46001</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>45580</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19832,7 +19832,7 @@
         <v>45180</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>46190</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19978,7 +19978,7 @@
         <v>46191</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>45056</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20124,7 +20124,7 @@
         <v>46196</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>44571</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20270,7 +20270,7 @@
         <v>45631</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
         <v>45636</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>44624</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>46202</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>44586</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>46202</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>44686</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>44816</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>45108</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>45114</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>45219</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>44568</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>46254</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>46258</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>45148</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>46258</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>46258</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>46258</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>45119</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>46258</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21730,7 +21730,7 @@
         <v>46258</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>45947</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         <v>44760</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>45307</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>44680</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>45754</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>45468</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
         <v>45187</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>45611</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>45943</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>45943</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>46266</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>45439</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>45243</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         <v>45225</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>46269</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22898,7 +22898,7 @@
         <v>46045</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>44844</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>45310</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45502</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>46273</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>46231</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>44812</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>45266</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>45225</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>46274</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>46274</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23706,7 +23706,7 @@
         <v>46232</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
         <v>45104</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>45565</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23925,7 +23925,7 @@
         <v>46237</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>46266</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>46045</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>45279</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>45943</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>46282</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>46282</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>44530</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>46282</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>46282</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>44797</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24728,7 +24728,7 @@
         <v>46245</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>44983</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>45091</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
         <v>45330</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>44728</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>45501</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>45270</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>46251</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>46261</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>45106</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25463,7 +25463,7 @@
         <v>45607</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>44607</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25609,7 +25609,7 @@
         <v>44742</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>45114</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25755,7 +25755,7 @@
         <v>44568</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>45114</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25901,7 +25901,7 @@
         <v>45163</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>45028</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26047,7 +26047,7 @@
         <v>45376</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26120,7 +26120,7 @@
         <v>45007</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>45461</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26271,7 +26271,7 @@
         <v>45309</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>44525</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>45439</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>45266</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>45238</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>45068</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>44531</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26787,7 +26787,7 @@
         <v>44533</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26860,7 +26860,7 @@
         <v>45567</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26933,7 +26933,7 @@
         <v>45072</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>45197</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>44962</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>44743</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>45219</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>45152</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>44897</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>45118</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>44923</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>45519</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>44622</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>45412</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27819,7 +27819,7 @@
         <v>45782</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27892,7 +27892,7 @@
         <v>45243</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27965,7 +27965,7 @@
         <v>44609</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>44230</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28111,7 +28111,7 @@
         <v>44621</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>45457</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28257,7 +28257,7 @@
         <v>44959</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>45457</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28403,7 +28403,7 @@
         <v>44959</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>45602</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>45575</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>44959</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>45733</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>46069</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>46069</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>46069</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>46071</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29060,7 +29060,7 @@
         <v>46092</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>46121</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>

--- a/Översikt KARLSHAMN.xlsx
+++ b/Översikt KARLSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>44897</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45170</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>46218</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>46150</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45376</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45310</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>44497</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>45187</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>45934</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>46211</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>46184</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>44621</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45603</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>46092</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>45028</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>45169</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>44897</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>46092</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>44595</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>45118</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>44943</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>45782</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>45068</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>44901</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>45826</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>45104</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>46282</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>44655</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>44862</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>45898</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>46121</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>44722</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>44680</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>44476</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>44812</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>44525</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>44579</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>44563</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>44509</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>44480</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>44834</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>44742</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>44579</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>44834</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>44563</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>44581</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>44523</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44582</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>44776</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>44776</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>44489</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44580</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>44796</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>44522</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>44489</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44489</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>44525</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>44526</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>44484</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>44487</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>44812</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>44743</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>44680</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>45611</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>44903</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>45119</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>45351</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>45007</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>45051</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>45051</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>45205</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>45448</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>45412</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>44962</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>45180</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>45246</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>45246</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>45894</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>45903</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>45894</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>45219</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>44935</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>44895</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>44952</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>44952</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>45550</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>45898</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>45898</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>45898</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>44686</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>45870</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>44845</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         <v>45636</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>45967</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>46041</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>45905</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>45908</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>45908</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>44797</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>45911</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>45796</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         <v>45187</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>45104</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>45600</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>45166</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>45212</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
         <v>45918</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>45028</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>45805</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>46055</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>45926</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>45911</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>44480</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>45926</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>44649</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>45266</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>45461</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>45987</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>45937</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>45810</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>45429</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>45939</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         <v>45687</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>45229</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>44983</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>44970</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>45950</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>45953</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
         <v>46083</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
         <v>45813</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>45813</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11314,7 +11314,7 @@
         <v>45813</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>45813</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>45813</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11533,7 +11533,7 @@
         <v>45954</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         <v>45601</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>45205</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>45205</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>46097</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>45632</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>45967</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>45967</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>45400</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12200,7 +12200,7 @@
         <v>46097</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>46100</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>46104</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12419,7 +12419,7 @@
         <v>44624</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>45468</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>46106</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>46106</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>45108</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>45240</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>45981</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>45310</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>45981</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>45824</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>45114</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>45953</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>45953</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13383,7 +13383,7 @@
         <v>46113</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>46113</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>46113</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>45824</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>45824</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>45986</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>44943</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>45917</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13967,7 +13967,7 @@
         <v>44568</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>46122</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>45732</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>45826</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         <v>45072</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
         <v>46001</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
         <v>46001</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>45114</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>44812</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>45884</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>45743</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>45588</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>45501</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>45918</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>45151</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>45937</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>45975</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>45254</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15296,7 +15296,7 @@
         <v>45919</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>44797</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>45035</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>45884</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>45845</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>45719</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>45553</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>45846</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>44897</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15953,7 +15953,7 @@
         <v>45716</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>45219</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>45849</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>45439</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>45152</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>45855</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>45540</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>44959</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         <v>45846</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>45789</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16683,7 +16683,7 @@
         <v>45405</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>45270</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>45717</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>45848</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>45225</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>45330</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>45238</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>45782</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>45898</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>45148</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>45737</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>45279</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>46051</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>46149</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>45841</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>45118</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>44923</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>45580</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>45106</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>45846</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>44622</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>44518</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>45090</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>46161</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>45874</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>45457</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>45770</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>45163</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>45519</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>45091</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18883,7 +18883,7 @@
         <v>45722</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>45037</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>46164</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>44480</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
         <v>45757</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>44981</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>46164</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>46164</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>46170</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19545,7 +19545,7 @@
         <v>46170</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>46170</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19691,7 +19691,7 @@
         <v>46170</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19764,7 +19764,7 @@
         <v>46170</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19837,7 +19837,7 @@
         <v>44586</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>44568</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19983,7 +19983,7 @@
         <v>44607</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>45617</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>46174</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>44525</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>45841</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20348,7 +20348,7 @@
         <v>44531</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
         <v>46181</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>46181</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20567,7 +20567,7 @@
         <v>46190</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20640,7 +20640,7 @@
         <v>46001</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>46191</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20786,7 +20786,7 @@
         <v>44571</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>46196</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>45009</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>45376</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>45148</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         <v>45307</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>45056</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21297,7 +21297,7 @@
         <v>45607</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>45631</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21443,7 +21443,7 @@
         <v>44609</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>45054</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>44812</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>46202</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>46202</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>45068</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>45740</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21959,7 +21959,7 @@
         <v>46258</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22032,7 +22032,7 @@
         <v>46258</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22105,7 +22105,7 @@
         <v>44533</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22178,7 +22178,7 @@
         <v>46258</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22251,7 +22251,7 @@
         <v>46258</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22324,7 +22324,7 @@
         <v>46258</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>46258</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22470,7 +22470,7 @@
         <v>45947</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22543,7 +22543,7 @@
         <v>45943</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>45943</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>45502</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>46266</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>46269</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22908,7 +22908,7 @@
         <v>45138</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45079</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>44530</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23127,7 +23127,7 @@
         <v>46273</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>46045</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>44971</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23351,7 +23351,7 @@
         <v>46274</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>46274</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23497,7 +23497,7 @@
         <v>45373</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23570,7 +23570,7 @@
         <v>46231</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>46232</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23716,7 +23716,7 @@
         <v>46266</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23789,7 +23789,7 @@
         <v>46237</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>45943</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>44943</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>45114</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24081,7 +24081,7 @@
         <v>46282</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>46282</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>46282</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>46282</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>45550</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>44742</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24519,7 +24519,7 @@
         <v>44827</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24592,7 +24592,7 @@
         <v>45519</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>45243</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>45104</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>44823</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>45307</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24957,7 +24957,7 @@
         <v>44939</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>44939</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>44939</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25176,7 +25176,7 @@
         <v>44760</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>44952</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25322,7 +25322,7 @@
         <v>45147</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>46245</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>45439</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>44924</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>45148</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25692,7 +25692,7 @@
         <v>46261</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25765,7 +25765,7 @@
         <v>44623</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25838,7 +25838,7 @@
         <v>46251</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25911,7 +25911,7 @@
         <v>45225</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25984,7 +25984,7 @@
         <v>46294</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>45631</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>45197</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>45754</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>46045</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>46294</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>46254</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>45163</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
         <v>45309</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>45596</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>45596</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26787,7 +26787,7 @@
         <v>45567</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26860,7 +26860,7 @@
         <v>45565</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26933,7 +26933,7 @@
         <v>45236</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>45114</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>44844</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>44660</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>44816</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>44728</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>45344</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>45400</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>44946</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>45266</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>45412</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27746,7 +27746,7 @@
         <v>45782</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27819,7 +27819,7 @@
         <v>44609</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27892,7 +27892,7 @@
         <v>45243</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27965,7 +27965,7 @@
         <v>44230</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>44621</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28111,7 +28111,7 @@
         <v>45457</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>44959</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28257,7 +28257,7 @@
         <v>45457</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>44959</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28403,7 +28403,7 @@
         <v>45602</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>45575</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>44959</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>45733</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>46069</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>46069</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>46069</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>46071</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>46092</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29060,7 +29060,7 @@
         <v>46121</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>

--- a/Översikt KARLSHAMN.xlsx
+++ b/Översikt KARLSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>44897</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45170</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>46218</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>46150</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45376</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45310</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>44497</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>45187</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>45934</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>46211</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>46184</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>44621</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45603</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>46092</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>45028</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>45169</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>44897</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>46092</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>44595</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>45118</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>44943</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>45782</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>45068</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>44901</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>45826</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>45104</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>46282</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>44655</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>44862</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>45898</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>46121</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>44722</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>44680</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>44476</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>44812</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>44525</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>44579</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>44563</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>44509</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>44480</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>44834</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>44742</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>44579</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>44834</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>44563</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>44581</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>44523</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44582</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>44776</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>44776</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>44489</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44580</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>44796</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>44522</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>44489</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44489</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>44525</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>44526</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>44484</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>44487</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>44812</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>44743</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>44680</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>45611</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>44903</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>45119</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>45351</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>45007</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>45051</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>45051</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>45205</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>45448</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>45412</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>44962</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>45180</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>45246</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>45246</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>45894</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>45903</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>45894</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>45219</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>44935</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>44895</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>44952</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>44952</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>45550</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>45898</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>45898</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>45898</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>44686</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>45870</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>44845</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         <v>45636</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>45967</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>46041</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>45905</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>45908</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>45908</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>44797</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>45911</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>45796</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         <v>45187</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>45104</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>45600</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>45166</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>45212</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
         <v>45918</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>45028</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>45805</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>46055</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>45926</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>45911</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>44480</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>45926</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>44649</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>45266</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>45461</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>45987</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>45937</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>45810</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>45429</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>45939</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         <v>45687</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>45229</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>44983</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>44970</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>45950</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>45953</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
         <v>46083</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
         <v>45813</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>45813</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11314,7 +11314,7 @@
         <v>45813</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>45813</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>45813</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11533,7 +11533,7 @@
         <v>45954</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         <v>45601</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>45205</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>45205</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>46097</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>45632</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>45967</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>45967</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>45400</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12200,7 +12200,7 @@
         <v>46097</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>46100</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>46104</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12419,7 +12419,7 @@
         <v>44624</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>45468</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>46106</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>46106</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>45108</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>45240</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>45981</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>45310</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13018,7 +13018,7 @@
         <v>45981</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>45824</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>45114</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>45953</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>45953</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13383,7 +13383,7 @@
         <v>46113</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>46113</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>46113</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>45824</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>45824</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>45986</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>44943</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>45917</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13967,7 +13967,7 @@
         <v>44568</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>46122</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>45732</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>45826</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         <v>45072</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
         <v>46001</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
         <v>46001</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>45114</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>44812</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>45884</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>45743</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>45588</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>45501</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>45918</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>45151</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>45937</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>45975</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>45254</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15296,7 +15296,7 @@
         <v>45919</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>44797</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>45035</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>45884</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>45845</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>45719</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>45553</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>45846</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>44897</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15953,7 +15953,7 @@
         <v>45716</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>45219</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>45849</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>45439</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>45152</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>45855</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>45540</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>44959</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         <v>45846</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>45789</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16683,7 +16683,7 @@
         <v>45405</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>45270</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>45717</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>45848</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>45225</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>45330</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>45238</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>45782</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>45898</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>45148</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>45737</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>45279</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>46051</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>46149</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>45841</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>45118</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>44923</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>45580</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>45106</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>45846</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>44622</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>44518</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>45090</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>46161</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>45874</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>45457</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>45770</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>45163</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>45519</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>45091</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18883,7 +18883,7 @@
         <v>45722</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>45037</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>46164</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>44480</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
         <v>45757</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>44981</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>46164</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>46164</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>46170</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19545,7 +19545,7 @@
         <v>46170</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>46170</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19691,7 +19691,7 @@
         <v>46170</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19764,7 +19764,7 @@
         <v>46170</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19837,7 +19837,7 @@
         <v>44586</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>44568</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19983,7 +19983,7 @@
         <v>44607</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>45617</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>46174</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>44525</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>45841</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20348,7 +20348,7 @@
         <v>44531</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
         <v>46181</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>46181</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20567,7 +20567,7 @@
         <v>46190</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20640,7 +20640,7 @@
         <v>46001</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>46191</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20786,7 +20786,7 @@
         <v>44571</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>46196</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>45009</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>45376</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>45148</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         <v>45307</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>45056</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21297,7 +21297,7 @@
         <v>45607</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>45631</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21443,7 +21443,7 @@
         <v>44609</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>45054</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>44812</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>46202</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>46202</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>45068</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>45740</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21959,7 +21959,7 @@
         <v>46258</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22032,7 +22032,7 @@
         <v>46258</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22105,7 +22105,7 @@
         <v>44533</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22178,7 +22178,7 @@
         <v>46258</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22251,7 +22251,7 @@
         <v>46258</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22324,7 +22324,7 @@
         <v>46258</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>46258</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22470,7 +22470,7 @@
         <v>45947</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22543,7 +22543,7 @@
         <v>45943</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>45943</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>45502</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>46266</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>46269</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22908,7 +22908,7 @@
         <v>45138</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45079</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>44530</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23127,7 +23127,7 @@
         <v>46273</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>46045</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>44971</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23351,7 +23351,7 @@
         <v>46274</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>46274</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23497,7 +23497,7 @@
         <v>45373</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23570,7 +23570,7 @@
         <v>46231</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>46232</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23716,7 +23716,7 @@
         <v>46266</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23789,7 +23789,7 @@
         <v>46237</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>45943</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>44943</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>45114</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24081,7 +24081,7 @@
         <v>46282</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>46282</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>46282</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>46282</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>45550</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>44742</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24519,7 +24519,7 @@
         <v>44827</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24592,7 +24592,7 @@
         <v>45519</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>45243</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>45104</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>44823</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>45307</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24957,7 +24957,7 @@
         <v>44939</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>44939</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>44939</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25176,7 +25176,7 @@
         <v>44760</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>44952</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25322,7 +25322,7 @@
         <v>45147</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>46245</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>45439</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>44924</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>45148</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25692,7 +25692,7 @@
         <v>46261</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25765,7 +25765,7 @@
         <v>44623</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25838,7 +25838,7 @@
         <v>46251</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25911,7 +25911,7 @@
         <v>45225</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25984,7 +25984,7 @@
         <v>46294</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>45631</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>45197</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>45754</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>46045</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>46294</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>46254</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>45163</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
         <v>45309</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>45596</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>45596</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26787,7 +26787,7 @@
         <v>45567</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26860,7 +26860,7 @@
         <v>45565</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26933,7 +26933,7 @@
         <v>45236</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>45114</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>44844</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>44660</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>44816</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>44728</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>45344</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>45400</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>44946</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>45266</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>45412</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27746,7 +27746,7 @@
         <v>45782</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27819,7 +27819,7 @@
         <v>44609</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27892,7 +27892,7 @@
         <v>45243</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27965,7 +27965,7 @@
         <v>44230</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>44621</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28111,7 +28111,7 @@
         <v>45457</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>44959</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28257,7 +28257,7 @@
         <v>45457</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>44959</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28403,7 +28403,7 @@
         <v>45602</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>45575</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>44959</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>45733</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>46069</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>46069</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>46069</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>46071</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>46092</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29060,7 +29060,7 @@
         <v>46121</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>

--- a/Översikt KARLSHAMN.xlsx
+++ b/Översikt KARLSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>44897</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45170</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>46218</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>46150</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45310</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>45376</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>44497</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>45187</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>45934</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>46211</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>44621</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>46184</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45603</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>46092</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>45169</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>45028</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>44897</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>46092</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>44595</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>44901</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>45118</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>45826</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>44655</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>45104</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>45068</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>44862</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44943</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>45782</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>46282</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>45898</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>46121</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>44722</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>44680</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>44812</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>44525</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>44579</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>44509</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>44563</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>44480</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>44834</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>44742</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>44579</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>44834</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>44563</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>44581</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>44523</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>44489</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44525</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>44526</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>44582</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>44484</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44489</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>44776</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>44776</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>44489</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44796</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>44580</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>44522</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>44487</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>44812</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>45007</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>45540</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>45461</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>45631</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>45412</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>44959</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>45309</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>45205</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>44525</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6753,7 +6753,7 @@
         <v>45439</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6826,7 +6826,7 @@
         <v>45090</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         <v>45229</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>45550</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>45266</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>45238</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>45068</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>44531</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>44533</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>45567</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>45240</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>44970</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>45400</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>45400</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>45072</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>45197</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>44962</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>44743</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>45448</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>45841</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>45236</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>45166</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>44935</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>45219</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>45148</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>45152</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>44895</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>44939</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>44897</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>45118</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>45898</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>45898</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         <v>45898</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>45870</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>44981</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>44480</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>44923</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
         <v>44518</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>45905</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>45373</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>44480</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9781,7 +9781,7 @@
         <v>45519</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>44622</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>45519</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>45412</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>45351</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>45212</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>45911</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>44939</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>45114</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>45429</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>45009</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>45405</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>44943</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>45918</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>45243</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>44609</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         <v>45580</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>45180</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>45926</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>44623</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>45911</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>45056</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
         <v>45926</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
         <v>44609</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11538,7 +11538,7 @@
         <v>44571</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>45631</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11684,7 +11684,7 @@
         <v>45550</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11757,7 +11757,7 @@
         <v>45636</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>45051</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>45051</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>44624</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>44660</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>44686</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12200,7 +12200,7 @@
         <v>45600</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>45104</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>44816</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12419,7 +12419,7 @@
         <v>45108</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>45054</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>45937</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
         <v>45114</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>45805</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>45205</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>45205</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         <v>45219</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13003,7 +13003,7 @@
         <v>45810</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>45939</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13149,7 +13149,7 @@
         <v>44952</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13222,7 +13222,7 @@
         <v>44952</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>44568</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13368,7 +13368,7 @@
         <v>45740</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>45813</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>45813</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13587,7 +13587,7 @@
         <v>45813</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>45813</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         <v>45813</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>45344</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>45148</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
         <v>45119</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
         <v>45950</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14098,7 +14098,7 @@
         <v>45824</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>45824</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>45307</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>44971</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>44946</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14468,7 +14468,7 @@
         <v>45826</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         <v>45601</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
         <v>44952</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>44903</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14765,7 +14765,7 @@
         <v>45953</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         <v>45954</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>45457</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>44760</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         <v>45307</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15130,7 +15130,7 @@
         <v>45254</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>44680</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>45754</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         <v>45967</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>45967</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15505,7 +15505,7 @@
         <v>45468</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>44797</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>45163</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>44649</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>45846</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>45719</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>45035</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>45845</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>45187</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>45147</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>45611</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>45722</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16381,7 +16381,7 @@
         <v>45849</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16454,7 +16454,7 @@
         <v>45632</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>45439</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>45148</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>45243</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>45855</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16819,7 +16819,7 @@
         <v>45138</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16892,7 +16892,7 @@
         <v>45225</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         <v>45737</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>44812</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>44844</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>45310</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>45502</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>45841</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17408,7 +17408,7 @@
         <v>45874</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         <v>44812</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17554,7 +17554,7 @@
         <v>44823</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>45266</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>44827</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>45687</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>45225</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>44845</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>45981</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18065,7 +18065,7 @@
         <v>45037</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18138,7 +18138,7 @@
         <v>45732</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>45981</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>44586</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>46097</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         <v>45104</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>45565</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>45079</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>45246</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>45246</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>45279</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18868,7 +18868,7 @@
         <v>45986</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>46104</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>44924</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>46106</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>46106</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19243,7 +19243,7 @@
         <v>45824</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19316,7 +19316,7 @@
         <v>45953</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         <v>45953</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
         <v>45917</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19535,7 +19535,7 @@
         <v>46113</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>46113</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19681,7 +19681,7 @@
         <v>46113</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19754,7 +19754,7 @@
         <v>45596</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>45596</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>44943</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>46122</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>44530</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>46001</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>46001</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>44797</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20348,7 +20348,7 @@
         <v>45846</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
         <v>45743</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>45884</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20567,7 +20567,7 @@
         <v>45894</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20640,7 +20640,7 @@
         <v>45975</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>45894</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20786,7 +20786,7 @@
         <v>45903</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>45918</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>45884</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>44983</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>45848</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         <v>45717</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>45919</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21297,7 +21297,7 @@
         <v>45716</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>45151</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21443,7 +21443,7 @@
         <v>45091</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>45553</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>45588</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>45330</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>44728</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>45501</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>45270</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         <v>45789</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>45106</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22100,7 +22100,7 @@
         <v>45607</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>44607</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22246,7 +22246,7 @@
         <v>45937</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22319,7 +22319,7 @@
         <v>44742</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>45114</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>46041</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
         <v>44568</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>45114</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>45163</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>45028</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>45376</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>45782</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>46055</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>46051</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>46149</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>45987</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>46083</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>45846</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>45770</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>46161</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>46097</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>46164</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23706,7 +23706,7 @@
         <v>46164</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
         <v>45757</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>46164</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23925,7 +23925,7 @@
         <v>46170</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>46170</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>46170</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>46170</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>45617</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>46170</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>46174</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>46181</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>46181</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>46001</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>46190</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24728,7 +24728,7 @@
         <v>46196</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>46202</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>46202</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>45947</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>46266</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>46269</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>46045</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>46273</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>46274</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>46274</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>46232</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>46266</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>46282</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>46282</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25750,7 +25750,7 @@
         <v>46282</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>46245</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25901,7 +25901,7 @@
         <v>46294</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>46294</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26047,7 +26047,7 @@
         <v>46045</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26120,7 +26120,7 @@
         <v>46300</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>45943</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>45943</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26339,7 +26339,7 @@
         <v>46300</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26412,7 +26412,7 @@
         <v>46300</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>46254</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>46300</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>45943</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26704,7 +26704,7 @@
         <v>46302</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26777,7 +26777,7 @@
         <v>46258</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26850,7 +26850,7 @@
         <v>46258</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26923,7 +26923,7 @@
         <v>46258</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
         <v>46258</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>46258</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>46258</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27215,7 +27215,7 @@
         <v>46251</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>46261</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>46282</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27434,7 +27434,7 @@
         <v>46231</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>45908</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>46303</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         <v>44230</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>44621</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>45457</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>44959</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>45457</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>44959</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>45602</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28169,7 +28169,7 @@
         <v>45575</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>44959</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>45733</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>46069</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>46069</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28534,7 +28534,7 @@
         <v>46069</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28607,7 +28607,7 @@
         <v>46071</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28680,7 +28680,7 @@
         <v>46092</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>46121</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>

--- a/Översikt KARLSHAMN.xlsx
+++ b/Översikt KARLSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>44897</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45170</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>46218</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>46150</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45310</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>45376</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>44497</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>45187</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>45934</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>46211</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>44621</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>46184</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45603</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>46092</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>45169</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>45028</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>44897</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>46092</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>44595</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>44901</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>45118</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>45826</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>44655</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>45104</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>45068</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>44862</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44943</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>45782</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>46282</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>45898</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>46121</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>44722</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>44680</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>44812</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>44525</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>44579</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>44509</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>44563</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>44480</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>44834</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>44742</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>44579</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>44834</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>44563</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>44581</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>44523</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>44489</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44525</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>44526</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>44582</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>44484</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44489</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>44776</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>44776</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>44489</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44796</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>44580</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>44522</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>44487</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>44812</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>45007</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>45540</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>45461</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>45631</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>45412</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>44959</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>45309</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>45205</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>44525</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6753,7 +6753,7 @@
         <v>45439</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6826,7 +6826,7 @@
         <v>45090</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         <v>45229</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>45550</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>45266</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>45238</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>45068</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>44531</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>44533</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>45567</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>45240</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>44970</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>45400</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>45400</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>45072</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>45197</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>44962</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>44743</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>45448</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>45841</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>45236</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>45166</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>44935</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>45219</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>45148</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>45152</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>44895</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>44939</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>44897</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>45118</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>45898</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>45898</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         <v>45898</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>45870</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>44981</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>44480</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>44923</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
         <v>44518</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>45905</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>45373</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>44480</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9781,7 +9781,7 @@
         <v>45519</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>44622</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>45519</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>45412</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>45351</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>45212</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>45911</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>44939</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>45114</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>45429</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>45009</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>45405</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>44943</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>45918</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>45243</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>44609</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         <v>45580</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>45180</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>45926</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>44623</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11246,7 +11246,7 @@
         <v>45911</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11319,7 +11319,7 @@
         <v>45056</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
         <v>45926</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
         <v>44609</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11538,7 +11538,7 @@
         <v>44571</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>45631</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11684,7 +11684,7 @@
         <v>45550</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11757,7 +11757,7 @@
         <v>45636</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>45051</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>45051</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>44624</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>44660</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>44686</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12200,7 +12200,7 @@
         <v>45600</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>45104</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>44816</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12419,7 +12419,7 @@
         <v>45108</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>45054</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>45937</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
         <v>45114</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>45805</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12784,7 +12784,7 @@
         <v>45205</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         <v>45205</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         <v>45219</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13003,7 +13003,7 @@
         <v>45810</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>45939</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13149,7 +13149,7 @@
         <v>44952</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13222,7 +13222,7 @@
         <v>44952</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>44568</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13368,7 +13368,7 @@
         <v>45740</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>45813</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>45813</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13587,7 +13587,7 @@
         <v>45813</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>45813</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         <v>45813</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>45344</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>45148</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
         <v>45119</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
         <v>45950</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14098,7 +14098,7 @@
         <v>45824</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>45824</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>45307</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>44971</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>44946</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14468,7 +14468,7 @@
         <v>45826</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14546,7 +14546,7 @@
         <v>45601</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
         <v>44952</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
         <v>44903</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14765,7 +14765,7 @@
         <v>45953</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         <v>45954</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>45457</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>44760</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         <v>45307</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15130,7 +15130,7 @@
         <v>45254</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>44680</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>45754</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         <v>45967</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>45967</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15505,7 +15505,7 @@
         <v>45468</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>44797</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>45163</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>44649</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>45846</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>45719</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>45035</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>45845</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>45187</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>45147</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>45611</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>45722</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16381,7 +16381,7 @@
         <v>45849</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16454,7 +16454,7 @@
         <v>45632</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>45439</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>45148</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>45243</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>45855</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16819,7 +16819,7 @@
         <v>45138</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16892,7 +16892,7 @@
         <v>45225</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         <v>45737</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>44812</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>44844</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>45310</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>45502</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>45841</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17408,7 +17408,7 @@
         <v>45874</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         <v>44812</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17554,7 +17554,7 @@
         <v>44823</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>45266</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>44827</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>45687</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>45225</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>44845</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>45981</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18065,7 +18065,7 @@
         <v>45037</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18138,7 +18138,7 @@
         <v>45732</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>45981</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>44586</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>46097</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         <v>45104</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>45565</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>45079</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>45246</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>45246</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>45279</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18868,7 +18868,7 @@
         <v>45986</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>46104</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>44924</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>46106</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>46106</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19243,7 +19243,7 @@
         <v>45824</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19316,7 +19316,7 @@
         <v>45953</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         <v>45953</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
         <v>45917</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19535,7 +19535,7 @@
         <v>46113</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>46113</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19681,7 +19681,7 @@
         <v>46113</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19754,7 +19754,7 @@
         <v>45596</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>45596</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>44943</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>46122</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>44530</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>46001</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>46001</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>44797</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20348,7 +20348,7 @@
         <v>45846</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20421,7 +20421,7 @@
         <v>45743</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         <v>45884</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20567,7 +20567,7 @@
         <v>45894</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20640,7 +20640,7 @@
         <v>45975</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20713,7 +20713,7 @@
         <v>45894</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20786,7 +20786,7 @@
         <v>45903</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20859,7 +20859,7 @@
         <v>45918</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>45884</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>44983</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>45848</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         <v>45717</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>45919</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21297,7 +21297,7 @@
         <v>45716</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>45151</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21443,7 +21443,7 @@
         <v>45091</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>45553</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>45588</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>45330</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>44728</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>45501</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>45270</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         <v>45789</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>45106</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22100,7 +22100,7 @@
         <v>45607</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>44607</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22246,7 +22246,7 @@
         <v>45937</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22319,7 +22319,7 @@
         <v>44742</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>45114</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>46041</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
         <v>44568</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>45114</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>45163</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>45028</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>45376</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>45782</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>46055</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>46051</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>46149</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>45987</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>46083</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>45846</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>45770</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>46161</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>46097</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>46164</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23706,7 +23706,7 @@
         <v>46164</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
         <v>45757</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>46164</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23925,7 +23925,7 @@
         <v>46170</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>46170</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>46170</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>46170</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>45617</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>46170</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>46174</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>46181</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>46181</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>46001</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>46190</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24728,7 +24728,7 @@
         <v>46196</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>46202</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>46202</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>45947</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>46266</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>46269</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>46045</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>46273</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>46274</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>46274</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>46232</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>46266</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
         <v>46282</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>46282</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25750,7 +25750,7 @@
         <v>46282</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>46245</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25901,7 +25901,7 @@
         <v>46294</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>46294</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26047,7 +26047,7 @@
         <v>46045</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26120,7 +26120,7 @@
         <v>46300</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>45943</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>45943</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26339,7 +26339,7 @@
         <v>46300</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26412,7 +26412,7 @@
         <v>46300</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>46254</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>46300</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>45943</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26704,7 +26704,7 @@
         <v>46302</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26777,7 +26777,7 @@
         <v>46258</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26850,7 +26850,7 @@
         <v>46258</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26923,7 +26923,7 @@
         <v>46258</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
         <v>46258</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>46258</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>46258</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27215,7 +27215,7 @@
         <v>46251</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>46261</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>46282</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27434,7 +27434,7 @@
         <v>46231</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>45908</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>46303</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         <v>44230</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>44621</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>45457</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>44959</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>45457</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>44959</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>45602</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28169,7 +28169,7 @@
         <v>45575</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>44959</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>45733</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>46069</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>46069</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28534,7 +28534,7 @@
         <v>46069</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28607,7 +28607,7 @@
         <v>46071</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28680,7 +28680,7 @@
         <v>46092</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>46121</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>

--- a/Översikt KARLSHAMN.xlsx
+++ b/Översikt KARLSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>44897</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45170</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>46218</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>46150</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45376</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45310</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>44497</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>45187</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>45934</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>46211</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>46184</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>44621</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45603</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>46092</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>45028</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>45169</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>44897</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>46092</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>44595</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>45068</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>44901</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>44943</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>45782</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>44655</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44862</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>45118</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>46282</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>45826</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>45104</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>45898</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>46121</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>44722</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>44680</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>44812</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>44525</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>44579</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>44563</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>44509</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>44834</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>44742</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>44579</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>44834</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>44563</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>44581</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>44523</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>44582</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>44776</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44776</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>44489</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>44580</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>44796</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44522</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>44489</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>44489</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>44525</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44526</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>44487</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>44812</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>44743</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>45119</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>45351</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>44680</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>45611</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>44903</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>45007</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>45205</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>45051</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>45051</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>45448</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>45412</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6826,7 +6826,7 @@
         <v>44962</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         <v>45180</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>45219</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>44935</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>44895</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>44952</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>44952</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>45550</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>44686</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>44845</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>45636</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>44797</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>45187</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>45246</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>45166</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>45028</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>45246</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>45212</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>44649</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>45266</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         <v>45461</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>45429</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>45687</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>45229</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>44983</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         <v>44970</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>45601</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>45205</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>45205</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>45632</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>45400</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>44624</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>45468</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>45108</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>45240</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>45310</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>45114</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>45884</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>45841</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>45553</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>45716</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>44568</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>45732</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>45846</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>45789</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>45072</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>45114</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>45717</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>45898</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>45848</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>45898</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>45898</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>44812</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         <v>45782</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         <v>45870</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>45905</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         <v>45501</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>45254</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v>45911</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>44797</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>45035</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         <v>45918</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>44897</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         <v>45219</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>46051</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11596,7 +11596,7 @@
         <v>45926</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>45911</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>46149</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>45439</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11888,7 +11888,7 @@
         <v>45152</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>45926</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         <v>45540</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>44959</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         <v>45937</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>45405</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>45270</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12399,7 +12399,7 @@
         <v>45939</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         <v>45225</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         <v>45330</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12618,7 +12618,7 @@
         <v>45950</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12691,7 +12691,7 @@
         <v>45238</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12764,7 +12764,7 @@
         <v>45953</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12837,7 +12837,7 @@
         <v>45846</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>45148</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>45954</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>46161</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>45770</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>45279</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>45967</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>45967</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>45118</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13504,7 +13504,7 @@
         <v>44923</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>45981</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>46164</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>45981</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>45580</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>45106</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>45757</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>44622</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>44518</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14166,7 +14166,7 @@
         <v>45986</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>46164</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14312,7 +14312,7 @@
         <v>45090</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14385,7 +14385,7 @@
         <v>46164</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>45917</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>45457</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>45163</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
         <v>45519</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         <v>45091</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>45722</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>45037</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>46001</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>46170</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>46170</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>46001</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>44981</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         <v>46170</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         <v>46170</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>46170</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>45894</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>45903</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>44568</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>45894</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15860,7 +15860,7 @@
         <v>44607</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15933,7 +15933,7 @@
         <v>44525</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>44531</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16079,7 +16079,7 @@
         <v>45617</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>46174</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>46041</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         <v>46181</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16371,7 +16371,7 @@
         <v>44571</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>45009</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>46181</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>46055</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>45376</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>45148</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>45307</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>45056</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>45607</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>45631</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
         <v>44609</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>45054</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>44812</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>45987</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17393,7 +17393,7 @@
         <v>45068</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17471,7 +17471,7 @@
         <v>46083</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>46190</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
         <v>46001</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>45740</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17763,7 +17763,7 @@
         <v>46097</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>46196</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>46097</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>44533</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>46104</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>46106</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18206,7 +18206,7 @@
         <v>46106</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>45824</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>45953</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         <v>45953</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>46113</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>46113</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>46113</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>44943</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>46122</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18868,7 +18868,7 @@
         <v>45502</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>46202</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>45138</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>46202</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19160,7 +19160,7 @@
         <v>45079</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19233,7 +19233,7 @@
         <v>44530</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>44971</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>45373</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>45884</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19530,7 +19530,7 @@
         <v>45743</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>45588</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         <v>45918</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>45151</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
         <v>45937</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>45975</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
         <v>45919</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20041,7 +20041,7 @@
         <v>44943</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20114,7 +20114,7 @@
         <v>45114</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20187,7 +20187,7 @@
         <v>45550</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>44742</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>44827</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>45519</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>45243</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>45104</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>44823</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20698,7 +20698,7 @@
         <v>45307</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20771,7 +20771,7 @@
         <v>44939</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20844,7 +20844,7 @@
         <v>44939</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>45947</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>44760</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>44952</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>45147</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21209,7 +21209,7 @@
         <v>45439</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21282,7 +21282,7 @@
         <v>46273</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21355,7 +21355,7 @@
         <v>46045</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>44924</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>46274</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>46274</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21647,7 +21647,7 @@
         <v>45148</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>46232</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>44623</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21866,7 +21866,7 @@
         <v>45225</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>45631</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>45197</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22085,7 +22085,7 @@
         <v>45754</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>45163</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>45309</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22304,7 +22304,7 @@
         <v>45596</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
         <v>45596</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22450,7 +22450,7 @@
         <v>45567</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22523,7 +22523,7 @@
         <v>45565</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22596,7 +22596,7 @@
         <v>45236</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         <v>46245</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>45114</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>44844</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22893,7 +22893,7 @@
         <v>44660</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>44816</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>44728</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         <v>45344</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23190,7 +23190,7 @@
         <v>46294</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23263,7 +23263,7 @@
         <v>45400</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23336,7 +23336,7 @@
         <v>44946</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>45266</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23482,7 +23482,7 @@
         <v>46045</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23555,7 +23555,7 @@
         <v>46294</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23628,7 +23628,7 @@
         <v>46254</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23701,7 +23701,7 @@
         <v>46258</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23774,7 +23774,7 @@
         <v>45943</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23847,7 +23847,7 @@
         <v>46300</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>45412</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>46258</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>46300</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>46258</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>46300</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>45943</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>45943</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>46258</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>46300</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>44609</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>46251</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24728,7 +24728,7 @@
         <v>45243</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>46258</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>46302</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>45908</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>46231</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>46258</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>46303</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>45104</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>45600</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>46261</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25463,7 +25463,7 @@
         <v>46308</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>46308</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25609,7 +25609,7 @@
         <v>45805</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>46266</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25755,7 +25755,7 @@
         <v>46266</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>45810</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25901,7 +25901,7 @@
         <v>45813</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>45813</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26047,7 +26047,7 @@
         <v>45813</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26120,7 +26120,7 @@
         <v>45813</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>45813</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>46282</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26339,7 +26339,7 @@
         <v>46282</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26412,7 +26412,7 @@
         <v>45824</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>45824</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>46269</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>46282</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26704,7 +26704,7 @@
         <v>46282</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26777,7 +26777,7 @@
         <v>46311</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26850,7 +26850,7 @@
         <v>45826</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>45845</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>45719</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>45846</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>45849</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>45855</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>45737</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         <v>45841</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>45874</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>44586</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>44230</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         <v>44621</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>45457</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>44959</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>45457</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>44959</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>45602</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>45575</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28169,7 +28169,7 @@
         <v>44959</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>45733</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>46069</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>46069</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>46069</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28534,7 +28534,7 @@
         <v>46071</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28607,7 +28607,7 @@
         <v>46092</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28680,7 +28680,7 @@
         <v>46121</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>

--- a/Översikt KARLSHAMN.xlsx
+++ b/Översikt KARLSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>44897</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>45170</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>46218</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>46150</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45376</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45310</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>44497</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>45187</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>45934</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>46211</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>46184</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>44621</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45603</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>46092</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>45028</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>45169</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>44897</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>46092</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>44595</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>45068</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>44901</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>44943</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>45782</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>44655</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>44862</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>45118</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>46282</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         <v>45826</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>45104</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>45898</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>46121</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>44722</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>44680</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>44812</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>44525</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>44579</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>44563</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>44509</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>44834</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>44742</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>44579</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>44834</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>44563</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>44581</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>44523</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>44582</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>44776</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44776</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>44489</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>44580</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>44796</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44522</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>44489</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>44489</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>44525</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44526</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>44487</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>44812</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>44743</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>45119</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>45351</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>44680</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>45611</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>44903</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>45007</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>45205</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>45051</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>45051</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>45448</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>45412</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6826,7 +6826,7 @@
         <v>44962</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         <v>45180</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>45219</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>44935</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>44895</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>44952</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>44952</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>45550</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>44686</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>44845</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>45636</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>44797</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>45187</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>45246</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>45166</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>45028</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>45246</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>45212</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>44649</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>45266</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         <v>45461</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>45429</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>45687</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>45229</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>44983</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         <v>44970</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>45601</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>45205</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>45205</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>45632</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>45400</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>44624</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>45468</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>45108</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>45240</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>45310</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>45114</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>45884</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>45841</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>45553</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>45716</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>44568</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>45732</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>45846</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>45789</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>45072</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>45114</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>45717</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>45898</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>45848</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>45898</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>45898</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>44812</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         <v>45782</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         <v>45870</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>45905</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         <v>45501</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>45254</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v>45911</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>44797</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>45035</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         <v>45918</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>44897</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         <v>45219</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>46051</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11596,7 +11596,7 @@
         <v>45926</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>45911</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>46149</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>45439</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11888,7 +11888,7 @@
         <v>45152</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>45926</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         <v>45540</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>44959</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         <v>45937</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>45405</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>45270</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12399,7 +12399,7 @@
         <v>45939</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         <v>45225</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         <v>45330</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12618,7 +12618,7 @@
         <v>45950</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12691,7 +12691,7 @@
         <v>45238</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12764,7 +12764,7 @@
         <v>45953</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12837,7 +12837,7 @@
         <v>45846</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>45148</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>45954</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>46161</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>45770</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>45279</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>45967</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>45967</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>45118</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13504,7 +13504,7 @@
         <v>44923</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>45981</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>46164</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>45981</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>45580</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>45106</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>45757</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>44622</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>44518</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14166,7 +14166,7 @@
         <v>45986</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>46164</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14312,7 +14312,7 @@
         <v>45090</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14385,7 +14385,7 @@
         <v>46164</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>45917</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>45457</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>45163</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
         <v>45519</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         <v>45091</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>45722</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>45037</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>46001</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>46170</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>46170</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>46001</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>44981</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         <v>46170</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         <v>46170</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>46170</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>45894</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>45903</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>44568</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>45894</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15860,7 +15860,7 @@
         <v>44607</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15933,7 +15933,7 @@
         <v>44525</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>44531</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16079,7 +16079,7 @@
         <v>45617</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>46174</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>46041</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         <v>46181</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16371,7 +16371,7 @@
         <v>44571</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>45009</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>46181</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>46055</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>45376</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>45148</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>45307</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>45056</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>45607</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>45631</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
         <v>44609</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>45054</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>44812</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>45987</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17393,7 +17393,7 @@
         <v>45068</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17471,7 +17471,7 @@
         <v>46083</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>46190</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
         <v>46001</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>45740</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17763,7 +17763,7 @@
         <v>46097</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>46196</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>46097</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>44533</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>46104</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>46106</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18206,7 +18206,7 @@
         <v>46106</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>45824</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>45953</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         <v>45953</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>46113</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>46113</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>46113</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>44943</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>46122</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18868,7 +18868,7 @@
         <v>45502</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>46202</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>45138</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>46202</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19160,7 +19160,7 @@
         <v>45079</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19233,7 +19233,7 @@
         <v>44530</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>44971</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>45373</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>45884</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19530,7 +19530,7 @@
         <v>45743</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>45588</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         <v>45918</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>45151</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
         <v>45937</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>45975</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
         <v>45919</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20041,7 +20041,7 @@
         <v>44943</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20114,7 +20114,7 @@
         <v>45114</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20187,7 +20187,7 @@
         <v>45550</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>44742</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>44827</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>45519</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20479,7 +20479,7 @@
         <v>45243</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>45104</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>44823</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20698,7 +20698,7 @@
         <v>45307</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20771,7 +20771,7 @@
         <v>44939</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20844,7 +20844,7 @@
         <v>44939</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>45947</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>44760</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         <v>44952</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>45147</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21209,7 +21209,7 @@
         <v>45439</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21282,7 +21282,7 @@
         <v>46273</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21355,7 +21355,7 @@
         <v>46045</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21428,7 +21428,7 @@
         <v>44924</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>46274</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>46274</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21647,7 +21647,7 @@
         <v>45148</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>46232</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>44623</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21866,7 +21866,7 @@
         <v>45225</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>45631</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>45197</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22085,7 +22085,7 @@
         <v>45754</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>45163</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>45309</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22304,7 +22304,7 @@
         <v>45596</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
         <v>45596</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22450,7 +22450,7 @@
         <v>45567</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22523,7 +22523,7 @@
         <v>45565</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22596,7 +22596,7 @@
         <v>45236</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         <v>46245</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>45114</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>44844</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22893,7 +22893,7 @@
         <v>44660</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>44816</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>44728</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         <v>45344</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23190,7 +23190,7 @@
         <v>46294</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23263,7 +23263,7 @@
         <v>45400</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23336,7 +23336,7 @@
         <v>44946</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>45266</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23482,7 +23482,7 @@
         <v>46045</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23555,7 +23555,7 @@
         <v>46294</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23628,7 +23628,7 @@
         <v>46254</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23701,7 +23701,7 @@
         <v>46258</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23774,7 +23774,7 @@
         <v>45943</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23847,7 +23847,7 @@
         <v>46300</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>45412</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>46258</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>46300</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>46258</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>46300</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>45943</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>45943</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>46258</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>46300</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>44609</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>46251</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24728,7 +24728,7 @@
         <v>45243</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>46258</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>46302</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>45908</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>46231</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>46258</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>46303</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>45104</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>45600</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>46261</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25463,7 +25463,7 @@
         <v>46308</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>46308</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25609,7 +25609,7 @@
         <v>45805</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>46266</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25755,7 +25755,7 @@
         <v>46266</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>45810</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25901,7 +25901,7 @@
         <v>45813</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>45813</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26047,7 +26047,7 @@
         <v>45813</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26120,7 +26120,7 @@
         <v>45813</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>45813</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>46282</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26339,7 +26339,7 @@
         <v>46282</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26412,7 +26412,7 @@
         <v>45824</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>45824</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>46269</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>46282</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26704,7 +26704,7 @@
         <v>46282</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26777,7 +26777,7 @@
         <v>46311</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26850,7 +26850,7 @@
         <v>45826</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>45845</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>45719</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>45846</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>45849</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>45855</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>45737</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         <v>45841</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>45874</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>44586</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>44230</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         <v>44621</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>45457</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>44959</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>45457</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>44959</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>45602</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>45575</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28169,7 +28169,7 @@
         <v>44959</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>45733</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>46069</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>46069</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>46069</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28534,7 +28534,7 @@
         <v>46071</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28607,7 +28607,7 @@
         <v>46092</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28680,7 +28680,7 @@
         <v>46121</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>

--- a/Översikt KARLSHAMN.xlsx
+++ b/Översikt KARLSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>44897</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>46218</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>46150</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>45170</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45310</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>45376</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>44497</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>45187</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>45934</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>46211</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>46184</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>44621</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45603</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>46092</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>45028</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>45169</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>44897</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>46092</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>44595</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>44943</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>45118</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>45782</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>45826</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>45104</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>46282</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>45068</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>44901</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>44655</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>44862</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>45898</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>46121</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>44722</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>44680</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>44812</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>44525</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>44579</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>44509</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>44563</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>44834</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>44742</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>44579</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>44834</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>44563</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>44581</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>44523</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>44582</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>44776</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44776</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>44580</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>44796</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>44522</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44525</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>44526</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>44812</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>45841</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>45412</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>45205</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>44983</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>45898</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>45091</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>45898</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>45898</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>45330</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>44728</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>45501</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>45870</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>45270</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>45905</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>46161</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>45106</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>45911</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>45607</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>46164</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>46164</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>44607</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>45757</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>46164</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
         <v>45918</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>44742</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>45114</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         <v>44568</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         <v>45114</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>45163</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         <v>45926</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>45911</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>45926</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>46170</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>46170</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>46170</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>46170</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>45617</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>45028</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>45376</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>46170</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>45937</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>45939</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>46174</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>45007</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>45550</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>45461</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>45950</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>46181</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>46181</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>45309</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>44525</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>45439</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>45953</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>45954</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>45266</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>45238</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         <v>45068</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>44531</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>46001</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>44533</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>45567</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         <v>46190</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>45967</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>45967</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>46196</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10433,7 +10433,7 @@
         <v>45072</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>45197</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>44962</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>44743</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>46202</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>46202</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>45240</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>45981</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>45981</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
         <v>45219</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
         <v>44970</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>45152</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11314,7 +11314,7 @@
         <v>44897</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>45118</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>45986</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11533,7 +11533,7 @@
         <v>45917</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         <v>45400</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>45400</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>44923</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>45947</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>45519</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>44622</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>45412</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12122,7 +12122,7 @@
         <v>46001</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12200,7 +12200,7 @@
         <v>46001</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>46045</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>45894</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>46232</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>45894</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12570,7 +12570,7 @@
         <v>45903</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>45243</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>44609</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>46041</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>46245</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>45600</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>45104</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>45448</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>46055</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>45805</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13305,7 +13305,7 @@
         <v>45810</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13378,7 +13378,7 @@
         <v>46294</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13451,7 +13451,7 @@
         <v>45813</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>45813</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>45813</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>45813</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>45813</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>45987</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         <v>45824</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>45824</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14035,7 +14035,7 @@
         <v>45826</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>46294</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>46300</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>46083</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>45943</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>45943</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>46300</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>46300</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>46254</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>46300</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>46097</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>44895</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>46097</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14989,7 +14989,7 @@
         <v>44939</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>45943</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>45846</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>45719</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15281,7 +15281,7 @@
         <v>45845</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>46302</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>46104</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>45849</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15573,7 +15573,7 @@
         <v>46258</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>46258</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>46258</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15792,7 +15792,7 @@
         <v>46106</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>46258</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>46106</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16021,7 +16021,7 @@
         <v>45824</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
         <v>45953</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16167,7 +16167,7 @@
         <v>45953</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>44981</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>45855</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>46258</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>46258</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         <v>46261</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>46113</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16683,7 +16683,7 @@
         <v>46113</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>46113</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>45737</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>44943</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>46231</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>45908</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>45841</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>46122</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>45874</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>46303</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>44586</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>45351</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>44939</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>45846</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>45743</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>45884</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>45975</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>46308</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>45918</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>45405</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>45884</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>45848</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45717</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>45919</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18440,7 +18440,7 @@
         <v>45716</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>45151</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>44943</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>45553</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>46266</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>46266</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
         <v>45588</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18951,7 +18951,7 @@
         <v>45789</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19024,7 +19024,7 @@
         <v>46311</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19097,7 +19097,7 @@
         <v>46269</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19170,7 +19170,7 @@
         <v>45937</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19243,7 +19243,7 @@
         <v>44623</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19316,7 +19316,7 @@
         <v>44609</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         <v>46273</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
         <v>46282</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19535,7 +19535,7 @@
         <v>46282</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>46251</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19681,7 +19681,7 @@
         <v>46282</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19754,7 +19754,7 @@
         <v>46282</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>45550</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>46308</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>45051</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>45051</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>46274</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>46274</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         <v>44660</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
         <v>45782</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>46316</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>46045</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>46051</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>45054</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>46149</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>45205</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>45205</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>44952</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44952</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>45740</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>45344</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>45846</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>45770</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>45307</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>44971</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>44946</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>45601</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>44952</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>44903</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>45457</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>45254</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         <v>44797</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>45163</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22100,7 +22100,7 @@
         <v>44649</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>45035</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22246,7 +22246,7 @@
         <v>45147</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22319,7 +22319,7 @@
         <v>45722</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>45632</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>45148</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
         <v>45138</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>44812</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>44823</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>44827</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>45687</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>44845</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>45037</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>45732</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45079</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>45246</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>45246</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>44924</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>45596</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>45596</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>45540</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>45631</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23706,7 +23706,7 @@
         <v>44959</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
         <v>45090</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>45229</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23925,7 +23925,7 @@
         <v>45236</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>45166</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>44935</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>45148</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>44518</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>45373</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24368,7 +24368,7 @@
         <v>45519</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24441,7 +24441,7 @@
         <v>45212</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24514,7 +24514,7 @@
         <v>45114</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
         <v>45429</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24660,7 +24660,7 @@
         <v>45009</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24733,7 +24733,7 @@
         <v>45580</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>45180</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>45056</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
         <v>44571</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>45631</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>45636</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>44624</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>44686</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>44816</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>45108</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25463,7 +25463,7 @@
         <v>45114</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>45219</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25609,7 +25609,7 @@
         <v>44568</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>45148</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25755,7 +25755,7 @@
         <v>45119</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>44760</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25901,7 +25901,7 @@
         <v>45307</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>44680</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26047,7 +26047,7 @@
         <v>45754</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26120,7 +26120,7 @@
         <v>45468</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>45187</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>45611</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26339,7 +26339,7 @@
         <v>45439</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26412,7 +26412,7 @@
         <v>45243</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>45225</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>44844</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>45310</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>45502</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>44812</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>45266</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>45225</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>45104</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>45565</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>45279</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>44530</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>44797</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         <v>44230</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44621</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>45457</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>44959</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         <v>45457</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>44959</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>45602</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>45575</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>44959</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>45733</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>46069</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28169,7 +28169,7 @@
         <v>46069</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>46069</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>46071</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>46092</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>46121</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>

--- a/Översikt KARLSHAMN.xlsx
+++ b/Översikt KARLSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>44897</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         <v>46218</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>46150</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>45170</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>45310</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>45376</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>44497</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>45187</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>45934</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>46211</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>46184</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>44621</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>45603</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>46092</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>45028</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>45169</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>44897</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>46092</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>44595</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>44943</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>45118</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>45782</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>45826</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>45104</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>46282</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>45068</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>44901</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>44655</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>44862</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>45898</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>46121</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>44722</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>44680</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>44812</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
         <v>44525</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>44579</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>44509</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>44563</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>44834</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>44742</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>44579</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>44834</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>44563</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>44581</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>44523</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>44582</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>44776</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44776</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>44580</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>44796</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>44522</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>44525</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>44526</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>44812</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>45841</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>45412</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>45205</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>44983</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>45898</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>45091</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>45898</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>45898</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>45330</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>44728</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>45501</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>45870</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>45270</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>45905</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>46161</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>45106</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>45911</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>45607</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>46164</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>46164</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>44607</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>45757</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>46164</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
         <v>45918</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7420,7 +7420,7 @@
         <v>44742</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>45114</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         <v>44568</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         <v>45114</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>45163</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         <v>45926</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>45911</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>45926</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>46170</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>46170</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>46170</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>46170</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>45617</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>45028</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>45376</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>46170</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>45937</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>45939</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>46174</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>45007</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>45550</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>45461</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>45950</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>46181</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>46181</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>45309</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>44525</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>45439</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>45953</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>45954</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>45266</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>45238</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         <v>45068</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>44531</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>46001</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>44533</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>45567</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         <v>46190</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>45967</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>45967</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>46196</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10433,7 +10433,7 @@
         <v>45072</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>45197</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>44962</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>44743</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>46202</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>46202</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>45240</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>45981</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>45981</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
         <v>45219</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
         <v>44970</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>45152</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11314,7 +11314,7 @@
         <v>44897</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>45118</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>45986</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11533,7 +11533,7 @@
         <v>45917</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         <v>45400</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>45400</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>44923</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>45947</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>45519</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>44622</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>45412</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12122,7 +12122,7 @@
         <v>46001</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12200,7 +12200,7 @@
         <v>46001</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>46045</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>45894</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>46232</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>45894</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12570,7 +12570,7 @@
         <v>45903</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>45243</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>44609</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>46041</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>46245</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>45600</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>45104</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>45448</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>46055</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>45805</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13305,7 +13305,7 @@
         <v>45810</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13378,7 +13378,7 @@
         <v>46294</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13451,7 +13451,7 @@
         <v>45813</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>45813</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>45813</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>45813</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>45813</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>45987</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         <v>45824</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>45824</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14035,7 +14035,7 @@
         <v>45826</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>46294</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>46300</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>46083</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>45943</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>45943</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>46300</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>46300</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>46254</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>46300</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>46097</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>44895</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>46097</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14989,7 +14989,7 @@
         <v>44939</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>45943</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>45846</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>45719</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15281,7 +15281,7 @@
         <v>45845</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>46302</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>46104</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>45849</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15573,7 +15573,7 @@
         <v>46258</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>46258</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>46258</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15792,7 +15792,7 @@
         <v>46106</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>46258</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>46106</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16021,7 +16021,7 @@
         <v>45824</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
         <v>45953</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16167,7 +16167,7 @@
         <v>45953</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>44981</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>45855</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
         <v>46258</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>46258</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         <v>46261</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>46113</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16683,7 +16683,7 @@
         <v>46113</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>46113</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>45737</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>44943</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>46231</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>45908</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         <v>45841</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>46122</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>45874</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>46303</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>44586</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>45351</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>44939</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>45846</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>45743</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>45884</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>45975</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>46308</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>45918</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>45405</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>45884</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>45848</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45717</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>45919</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18440,7 +18440,7 @@
         <v>45716</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>45151</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>44943</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>45553</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>46266</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>46266</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
         <v>45588</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18951,7 +18951,7 @@
         <v>45789</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19024,7 +19024,7 @@
         <v>46311</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19097,7 +19097,7 @@
         <v>46269</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19170,7 +19170,7 @@
         <v>45937</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19243,7 +19243,7 @@
         <v>44623</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19316,7 +19316,7 @@
         <v>44609</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         <v>46273</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19462,7 +19462,7 @@
         <v>46282</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19535,7 +19535,7 @@
         <v>46282</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>46251</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19681,7 +19681,7 @@
         <v>46282</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19754,7 +19754,7 @@
         <v>46282</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>45550</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>46308</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>45051</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>45051</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>46274</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>46274</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         <v>44660</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
         <v>45782</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>46316</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>46045</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>46051</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>45054</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>46149</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>45205</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>45205</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>44952</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44952</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>45740</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>45344</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>45846</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>45770</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>45307</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>44971</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>44946</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>45601</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>44952</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>44903</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>45457</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21881,7 +21881,7 @@
         <v>45254</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         <v>44797</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>45163</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22100,7 +22100,7 @@
         <v>44649</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>45035</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22246,7 +22246,7 @@
         <v>45147</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22319,7 +22319,7 @@
         <v>45722</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>45632</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>45148</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
         <v>45138</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>44812</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>44823</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>44827</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>45687</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>44845</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>45037</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>45732</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45079</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>45246</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>45246</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>44924</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>45596</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>45596</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>45540</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>45631</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23706,7 +23706,7 @@
         <v>44959</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
         <v>45090</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>45229</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23925,7 +23925,7 @@
         <v>45236</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>45166</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>44935</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>45148</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>44518</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>45373</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24368,7 +24368,7 @@
         <v>45519</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24441,7 +24441,7 @@
         <v>45212</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24514,7 +24514,7 @@
         <v>45114</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
         <v>45429</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24660,7 +24660,7 @@
         <v>45009</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24733,7 +24733,7 @@
         <v>45580</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>45180</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>45056</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
         <v>44571</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>45631</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>45636</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>44624</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>44686</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>44816</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>45108</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25463,7 +25463,7 @@
         <v>45114</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>45219</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25609,7 +25609,7 @@
         <v>44568</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>45148</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25755,7 +25755,7 @@
         <v>45119</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         <v>44760</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25901,7 +25901,7 @@
         <v>45307</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>44680</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26047,7 +26047,7 @@
         <v>45754</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26120,7 +26120,7 @@
         <v>45468</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26193,7 +26193,7 @@
         <v>45187</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>45611</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26339,7 +26339,7 @@
         <v>45439</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26412,7 +26412,7 @@
         <v>45243</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>45225</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26558,7 +26558,7 @@
         <v>44844</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>45310</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>45502</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>44812</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>45266</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>45225</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>45104</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>45565</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>45279</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>44530</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>44797</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         <v>44230</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44621</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>45457</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>44959</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         <v>45457</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>44959</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>45602</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>45575</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>44959</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>45733</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>46069</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28169,7 +28169,7 @@
         <v>46069</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>46069</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>46071</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>46092</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>46121</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
